--- a/yigongbao-parent/yigongbao-boot/src/main/resources/template/流转卡模板.xlsx
+++ b/yigongbao-parent/yigongbao-boot/src/main/resources/template/流转卡模板.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_Project\02_Personal\医工宝\.docs\temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_Project\02_Personal\医工宝\yigongbao-parent\yigongbao-boot\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F9F6C03-E2B7-4B59-9413-313DBCA2CAC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65046868-23C6-445D-954B-2216B6EDF8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="流转卡" sheetId="1" r:id="rId1"/>
@@ -225,7 +225,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -355,48 +355,90 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -886,7 +928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="11.75" customWidth="1"/>
@@ -897,82 +939,82 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="4"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="4"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="7"/>
     </row>
     <row r="3" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="4"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="7"/>
       <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="4"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="7"/>
       <c r="E4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="4" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="12" t="s">
+      <c r="B5" s="14"/>
+      <c r="C5" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="6" t="s">
+      <c r="D5" s="7"/>
+      <c r="E5" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="12" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="10"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="12" t="s">
+      <c r="A6" s="15"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
     </row>
     <row r="7" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="1" t="s">
@@ -994,7 +1036,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
@@ -1004,7 +1046,7 @@
       <c r="C8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="4" t="s">
         <v>43</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -1014,7 +1056,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="29.1" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -1024,17 +1066,17 @@
       <c r="C9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="15" t="s">
+      <c r="D9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>43</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:6" ht="66.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
@@ -1044,17 +1086,17 @@
       <c r="C10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="15" t="s">
+      <c r="D10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>43</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:6" ht="77.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="1" t="s">
         <v>24</v>
       </c>
@@ -1064,17 +1106,17 @@
       <c r="C11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="15" t="s">
+      <c r="D11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>43</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="1" t="s">
         <v>27</v>
       </c>
@@ -1084,17 +1126,17 @@
       <c r="C12" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="15" t="s">
+      <c r="D12" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>43</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
@@ -1104,10 +1146,10 @@
       <c r="C13" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="15" t="s">
+      <c r="D13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>43</v>
       </c>
       <c r="F13" s="1" t="s">
@@ -1124,10 +1166,10 @@
       <c r="C14" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="15" t="s">
+      <c r="D14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>43</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -1135,49 +1177,95 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="4"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="7"/>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="4"/>
+      <c r="B16" s="7"/>
       <c r="C16" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F17" s="4"/>
+      <c r="A17" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="18"/>
+      <c r="E17" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="18"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A18" s="21"/>
+      <c r="B18" s="21"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A19" s="20"/>
+      <c r="B19" s="20"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A20" s="20"/>
+      <c r="B20" s="20"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A21" s="20"/>
+      <c r="B21" s="20"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A24" s="20"/>
+      <c r="B24" s="20"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A25" s="20"/>
+      <c r="B25" s="20"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="22">
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="A15:F15"/>
@@ -1186,14 +1274,6 @@
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="F5:F6"/>
     <mergeCell ref="A5:B6"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.39" top="0.2" bottom="0.39" header="0.3" footer="0.3"/>

--- a/yigongbao-parent/yigongbao-boot/src/main/resources/template/流转卡模板.xlsx
+++ b/yigongbao-parent/yigongbao-boot/src/main/resources/template/流转卡模板.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_Project\02_Personal\医工宝\yigongbao-parent\yigongbao-boot\src\main\resources\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65046868-23C6-445D-954B-2216B6EDF8CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77BA3B2D-F54C-4E6A-AB60-1FD77B1419FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4476" yWindow="4440" windowWidth="21600" windowHeight="11292" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="流转卡" sheetId="1" r:id="rId1"/>
@@ -385,7 +385,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -404,14 +404,32 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -425,21 +443,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -928,45 +931,45 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.75" customWidth="1"/>
-    <col min="2" max="3" width="20.5" customWidth="1"/>
-    <col min="4" max="4" width="27.375" customWidth="1"/>
-    <col min="5" max="5" width="32.25" customWidth="1"/>
-    <col min="6" max="6" width="21.5" customWidth="1"/>
+    <col min="1" max="1" width="11.77734375" customWidth="1"/>
+    <col min="2" max="3" width="20.44140625" customWidth="1"/>
+    <col min="4" max="4" width="27.33203125" customWidth="1"/>
+    <col min="5" max="5" width="32.21875" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:6" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="7"/>
-    </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="6" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="13"/>
+    </row>
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="7"/>
-    </row>
-    <row r="3" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="8" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="13"/>
+    </row>
+    <row r="3" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D3" s="7"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="13"/>
       <c r="E3" s="1" t="s">
         <v>2</v>
       </c>
@@ -974,15 +977,15 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="8" t="s">
+    <row r="4" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="7"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="13"/>
       <c r="E4" s="1" t="s">
         <v>5</v>
       </c>
@@ -990,33 +993,33 @@
         <v>43</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="13" t="s">
+    <row r="5" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="6" t="s">
+      <c r="B5" s="20"/>
+      <c r="C5" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="10" t="s">
+      <c r="D5" s="13"/>
+      <c r="E5" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="15"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="6" t="s">
+      <c r="F5" s="18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="21"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-    </row>
-    <row r="7" spans="1:6" ht="15.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D6" s="13"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+    </row>
+    <row r="7" spans="1:6" ht="15.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -1036,7 +1039,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
@@ -1056,7 +1059,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:6" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>18</v>
       </c>
@@ -1076,7 +1079,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="66.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:6" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
@@ -1096,7 +1099,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="77.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:6" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>24</v>
       </c>
@@ -1116,7 +1119,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:6" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>27</v>
       </c>
@@ -1136,7 +1139,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>30</v>
       </c>
@@ -1156,7 +1159,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>33</v>
       </c>
@@ -1176,21 +1179,21 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A15" s="8" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="7"/>
-    </row>
-    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="8" t="s">
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="13"/>
+    </row>
+    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="7"/>
+      <c r="B16" s="13"/>
       <c r="C16" s="1" t="s">
         <v>38</v>
       </c>
@@ -1204,59 +1207,95 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B17" s="7"/>
+    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B17" s="13"/>
       <c r="C17" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="18"/>
-      <c r="E17" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="F17" s="18"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A18" s="21"/>
-      <c r="B18" s="21"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A19" s="20"/>
-      <c r="B19" s="20"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A20" s="20"/>
-      <c r="B20" s="20"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A21" s="20"/>
-      <c r="B21" s="20"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A22" s="20"/>
-      <c r="B22" s="20"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A24" s="20"/>
-      <c r="B24" s="20"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A25" s="20"/>
-      <c r="B25" s="20"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A5:B6"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="A24:B24"/>
     <mergeCell ref="A25:B25"/>
@@ -1273,7 +1312,11 @@
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="E5:E6"/>
     <mergeCell ref="F5:F6"/>
-    <mergeCell ref="A5:B6"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.39" top="0.2" bottom="0.39" header="0.3" footer="0.3"/>
